--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484581_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484581_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3027</v>
+        <v>5.6126</v>
       </c>
       <c r="E2" t="n">
-        <v>1.976</v>
+        <v>1.7565</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3268</v>
+        <v>3.8561</v>
       </c>
       <c r="G2" t="n">
         <v>2.0019</v>
@@ -610,13 +610,13 @@
         <v>3.1154</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9893</v>
+        <v>0.2992</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0521</v>
+        <v>-0.1674</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9373</v>
+        <v>0.4666</v>
       </c>
       <c r="V2" t="n">
         <v>2.212</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.394</v>
+        <v>3.9491</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7036</v>
+        <v>2.1844</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6904</v>
+        <v>1.7647</v>
       </c>
       <c r="G3" t="n">
         <v>1.6161</v>
@@ -688,13 +688,13 @@
         <v>2.3823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6827</v>
+        <v>-0.1276</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8446</v>
+        <v>-0.3639</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1619</v>
+        <v>0.2362</v>
       </c>
       <c r="V3" t="n">
         <v>1.9109</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. HYLLA</t>
+          <t>C. GARCIA SAHUQUILLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2712</v>
+        <v>3.5716</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.59</v>
+        <v>2.3788</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8612</v>
+        <v>1.1928</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4845</v>
+        <v>4.4277</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1802</v>
+        <v>2.7416</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6957</v>
+        <v>1.6861</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6762</v>
+        <v>4.1411</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9165</v>
+        <v>2.1983</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2404</v>
+        <v>1.9428</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8083</v>
+        <v>0.2866</v>
       </c>
       <c r="N4" t="n">
-        <v>1.2637</v>
+        <v>0.5433</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5446</v>
+        <v>-0.2567</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1833</v>
+        <v>-0.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0995</v>
+        <v>-2.0158</v>
       </c>
       <c r="R4" t="n">
         <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3312</v>
+        <v>0.1885</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1666</v>
+        <v>-0.0788</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1645</v>
+        <v>0.2673</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9346</v>
+        <v>-0.3115</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.3324</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9346</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. GARCIA SAHUQUILLO</t>
+          <t>L. HYLLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1235</v>
+        <v>3.3242</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9802</v>
+        <v>-0.8095</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1433</v>
+        <v>4.1337</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4277</v>
+        <v>2.4845</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7416</v>
+        <v>3.1802</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6861</v>
+        <v>-0.6957</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1411</v>
+        <v>0.6762</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1983</v>
+        <v>1.9165</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9428</v>
+        <v>-1.2404</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2866</v>
+        <v>1.8083</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5433</v>
+        <v>1.2637</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2567</v>
+        <v>0.5446</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0158</v>
+        <v>-1.0995</v>
       </c>
       <c r="R5" t="n">
         <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2596</v>
+        <v>-0.2781</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4774</v>
+        <v>-0.3861</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2178</v>
+        <v>0.108</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3115</v>
+        <v>0.9346</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3324</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6439</v>
+        <v>0.9346</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. HINAREJOS GOMEZ</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7618</v>
+        <v>1.096</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5897</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8279</v>
+        <v>0.1902</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2174</v>
+        <v>2.1146</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7303</v>
+        <v>1.1303</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5128</v>
+        <v>0.9843</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6998</v>
+        <v>3.6016</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3408</v>
+        <v>2.2325</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.641</v>
+        <v>1.3692</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4824</v>
+        <v>-1.487</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6106</v>
+        <v>-1.1021</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1282</v>
+        <v>-0.3849</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.317</v>
+        <v>0.3533</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1101</v>
+        <v>0.0034</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2069</v>
+        <v>0.3499</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3219</v>
+        <v>0.6439</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.9658</v>
       </c>
       <c r="X6" t="n">
         <v>-0.3219</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. LOZANO CATALA</t>
+          <t>H. HINAREJOS GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5796</v>
+        <v>0.8361</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4758</v>
+        <v>1.5897</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0554</v>
+        <v>-0.7536</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7643</v>
+        <v>1.2174</v>
       </c>
       <c r="H7" t="n">
-        <v>0.54</v>
+        <v>1.7303</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2243</v>
+        <v>-0.5128</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2292</v>
+        <v>1.6998</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2292</v>
+        <v>2.3408</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.641</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9935</v>
+        <v>-0.4824</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7692</v>
+        <v>-0.6106</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2243</v>
+        <v>0.1282</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4413</v>
+        <v>-0.2426</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3303</v>
+        <v>-0.1101</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1109</v>
+        <v>-0.1325</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>B. BREM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5161</v>
+        <v>0.7487</v>
       </c>
       <c r="E8" t="n">
-        <v>0.425</v>
+        <v>-1.6556</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0911</v>
+        <v>2.4044</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1146</v>
+        <v>0.3404</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1303</v>
+        <v>1.9014</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9843</v>
+        <v>-1.561</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6016</v>
+        <v>-1.0361</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2325</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3692</v>
+        <v>-1.8814</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.487</v>
+        <v>1.3765</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1021</v>
+        <v>1.0561</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3849</v>
+        <v>0.3204</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0158</v>
+        <v>1.0995</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6651</v>
+        <v>-0.1833</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2266</v>
+        <v>-0.6912</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4774</v>
+        <v>-0.4363</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2508</v>
+        <v>-0.2549</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9658</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. BREM</t>
+          <t>S. LOZANO CATALA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2892</v>
+        <v>0.6594</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9169</v>
+        <v>-1.4208</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2062</v>
+        <v>2.0802</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3404</v>
+        <v>0.7643</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9014</v>
+        <v>0.54</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.561</v>
+        <v>0.2243</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0361</v>
+        <v>-0.2292</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8453000000000001</v>
+        <v>-0.2292</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8814</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3765</v>
+        <v>0.9935</v>
       </c>
       <c r="N9" t="n">
-        <v>1.0561</v>
+        <v>0.7692</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3204</v>
+        <v>0.2243</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0995</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>0.5498</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1507</v>
+        <v>-0.3614</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6976</v>
+        <v>-0.2753</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4531</v>
+        <v>-0.0862</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>N. BURJEL PEZZATTI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.135</v>
+        <v>0.5392</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7101</v>
+        <v>-0.1872</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5750999999999999</v>
+        <v>0.7264</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5302</v>
+        <v>1.2811</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.63</v>
+        <v>-0.2799</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1602</v>
+        <v>1.561</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4507</v>
+        <v>0.4191</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0338</v>
+        <v>-0.3409</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4169</v>
+        <v>0.76</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9205</v>
+        <v>0.862</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6638</v>
+        <v>0.0609</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2567</v>
+        <v>0.8011</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0995</v>
+        <v>2.3823</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6651</v>
+        <v>-0.1833</v>
       </c>
       <c r="R10" t="n">
         <v>2.5656</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6493</v>
+        <v>-0.5903</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2806</v>
+        <v>-0.4231</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3688</v>
+        <v>-0.1673</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.945</v>
+        <v>-2.5339</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5889</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. BURJEL PEZZATTI</t>
+          <t>A. VILLALBA MOLLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0693</v>
+        <v>-0.374</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6819</v>
+        <v>-2.1004</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7512</v>
+        <v>1.7264</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2811</v>
+        <v>0.7891</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2799</v>
+        <v>0.4045</v>
       </c>
       <c r="I11" t="n">
-        <v>1.561</v>
+        <v>0.3846</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4191</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3409</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.862</v>
+        <v>0.0305</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0609</v>
+        <v>-0.3541</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8011</v>
+        <v>0.3846</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3823</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1833</v>
+        <v>-2.7489</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5656</v>
+        <v>0.5498</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0603</v>
+        <v>0.1014</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.1101</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1425</v>
+        <v>0.2115</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.5339</v>
+        <v>0.9346</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.5339</v>
+        <v>0.9346</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. VILLALBA MOLLA</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3795</v>
+        <v>-1.0743</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1554</v>
+        <v>-0.2515</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7759</v>
+        <v>-0.8228</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7891</v>
+        <v>0.5302</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4045</v>
+        <v>-0.63</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3846</v>
+        <v>1.1602</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7586000000000001</v>
+        <v>2.4507</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7586000000000001</v>
+        <v>1.0338</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.4169</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0305</v>
+        <v>-1.9205</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3541</v>
+        <v>-1.6638</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3846</v>
+        <v>-0.2567</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1991</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.7489</v>
+        <v>-3.6651</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5498</v>
+        <v>2.5656</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0959</v>
+        <v>0.44</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1652</v>
+        <v>0.319</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2611</v>
+        <v>0.121</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9346</v>
+        <v>-0.945</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9346</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.0629</v>
+        <v>18.8886</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5646</v>
+        <v>2.3901</v>
       </c>
       <c r="F13" t="n">
         <v>16.4985</v>
@@ -1438,7 +1438,7 @@
         <v>17.8885</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3211000000000002</v>
+        <v>-0.3211000000000004</v>
       </c>
       <c r="J13" t="n">
         <v>16.3575</v>
@@ -1456,10 +1456,10 @@
         <v>1.0521</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1577000000000002</v>
+        <v>0.1577000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9162000000000006</v>
+        <v>-0.9162000000000003</v>
       </c>
       <c r="Q13" t="n">
         <v>-18.3257</v>
@@ -1468,13 +1468,13 @@
         <v>17.4095</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7349</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.8543</v>
+        <v>-2.0287</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1198</v>
+        <v>1.1196</v>
       </c>
       <c r="V13" t="n">
         <v>3.1468</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. FAJARDO PANOS</t>
+          <t>C. FAJARDO PAÑOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8855</v>
+        <v>0.6251</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7331</v>
+        <v>0.6251</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6186</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5271</v>
+        <v>0.6251</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.6332</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1061</v>
+        <v>0.6251</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4004</v>
+        <v>0.6251</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.1862</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7857</v>
+        <v>0.6251</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1267</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4471</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3204</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7489</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7489</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7355</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2904</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4451</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0717</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. FAJARDO PAÑOS</t>
+          <t>C. FAJARDO PANOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6251</v>
+        <v>0.5795</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6251</v>
+        <v>-1.1177</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.6972</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6251</v>
+        <v>-1.5271</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-2.6332</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6251</v>
+        <v>1.1061</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6251</v>
+        <v>-0.4004</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-1.1862</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6251</v>
+        <v>0.7857</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-1.1267</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-1.4471</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.3204</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.7489</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.7489</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.4295</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.0717</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="16">
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. POVEDA CASTELLO</t>
+          <t>R. RAMOS SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2746</v>
+        <v>-0.328</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2864</v>
+        <v>0.7356</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5611</v>
+        <v>-1.0635</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6798</v>
+        <v>0.9423</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9521</v>
+        <v>-1.8082</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2723</v>
+        <v>2.7505</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1887</v>
+        <v>2.6813</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3711</v>
+        <v>0.6036</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8176</v>
+        <v>2.0776</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8685</v>
+        <v>-1.7389</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.3232</v>
+        <v>-2.4118</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5452</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.7489</v>
+        <v>1.6493</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.681</v>
+        <v>-1.0995</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9321</v>
+        <v>2.7489</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3698</v>
+        <v>0.063</v>
       </c>
       <c r="T17" t="n">
-        <v>1.902</v>
+        <v>-0.8461</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4678</v>
+        <v>0.9091</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7842</v>
+        <v>-2.9826</v>
       </c>
       <c r="W17" t="n">
-        <v>2.8767</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0925</v>
+        <v>-2.9826</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LORENTE</t>
+          <t>F. FERRER I SEGURA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4703</v>
+        <v>-1.446</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6414</v>
+        <v>-1.1958</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1116</v>
+        <v>-0.2502</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0778</v>
+        <v>-1.4326</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.648</v>
+        <v>-2.4455</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4298</v>
+        <v>1.0129</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3556</v>
+        <v>0.4633</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2722</v>
+        <v>-0.2292</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0833</v>
+        <v>0.6925</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4333</v>
+        <v>-1.8959</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9202</v>
+        <v>-2.2163</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5131</v>
+        <v>0.3204</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0158</v>
+        <v>-1.8326</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8353</v>
+        <v>-0.1521</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3462</v>
+        <v>-0.1485</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4891</v>
+        <v>-0.0036</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3115</v>
+        <v>0.3219</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9554</v>
+        <v>0.3219</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. FERRER I SEGURA</t>
+          <t>M. POVEDA CASTELLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6486</v>
+        <v>-1.4955</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1958</v>
+        <v>-0.9636</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4527</v>
+        <v>-0.532</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4326</v>
+        <v>-1.6798</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4455</v>
+        <v>-1.9521</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0129</v>
+        <v>0.2723</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4633</v>
+        <v>1.1887</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2292</v>
+        <v>0.3711</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6925</v>
+        <v>0.8176</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8959</v>
+        <v>-2.8685</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.2163</v>
+        <v>-2.3232</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3204</v>
+        <v>-0.5452</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1833</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8326</v>
+        <v>-5.681</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6493</v>
+        <v>2.9321</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3547</v>
+        <v>1.149</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1485</v>
+        <v>0.652</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2061</v>
+        <v>0.497</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3219</v>
+        <v>1.7842</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3219</v>
+        <v>2.8767</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0925</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. RAMOS SAN SEBASTIAN</t>
+          <t>J. JIMENEZ LORENTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7004</v>
+        <v>-1.683</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0336</v>
+        <v>0.4491</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6668</v>
+        <v>-2.1321</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9423</v>
+        <v>-1.0778</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8082</v>
+        <v>-0.648</v>
       </c>
       <c r="I20" t="n">
-        <v>2.7505</v>
+        <v>-0.4298</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6813</v>
+        <v>1.3556</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6036</v>
+        <v>1.2722</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0776</v>
+        <v>0.0833</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7389</v>
+        <v>-2.4333</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.4118</v>
+        <v>-1.9202</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.5131</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6493</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0995</v>
+        <v>-2.0158</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7489</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3095</v>
+        <v>0.6226</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.6153</v>
+        <v>0.1539</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3059</v>
+        <v>0.4687</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.9826</v>
+        <v>-0.3115</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.9826</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5899</v>
+        <v>-2.1019</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2402</v>
+        <v>-2.8556</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6503</v>
+        <v>0.7538</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2982</v>
@@ -2092,13 +2092,13 @@
         <v>2.5656</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7865</v>
+        <v>-0.2984</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.497</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0951</v>
+        <v>0.1985</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3219</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1993</v>
+        <v>-2.6835</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1084</v>
+        <v>-3.82</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9092</v>
+        <v>1.1365</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0438</v>
@@ -2170,13 +2170,13 @@
         <v>3.1154</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4294</v>
+        <v>0.0864</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6621</v>
+        <v>-0.3736</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2327</v>
+        <v>0.46</v>
       </c>
       <c r="V22" t="n">
         <v>0.1744</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4044</v>
+        <v>-3.4685</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2752</v>
+        <v>-3.4675</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1291</v>
+        <v>-0.0009</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6522</v>
@@ -2248,13 +2248,13 @@
         <v>0.1833</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6772</v>
+        <v>0.6131</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4751</v>
+        <v>0.2828</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2021</v>
+        <v>0.3303</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6127</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2525</v>
+        <v>-4.7456</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4649</v>
+        <v>-4.888</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2123</v>
+        <v>0.1424</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2064</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0032</v>
+        <v>0.5038</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8258</v>
+        <v>-0.2489</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8226</v>
+        <v>0.7526</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1267</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.0629</v>
+        <v>-16.7809</v>
       </c>
       <c r="E25" t="n">
-        <v>-16.4983</v>
+        <v>-16.4984</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5644</v>
+        <v>-0.2822999999999998</v>
       </c>
       <c r="G25" t="n">
         <v>-17.5672</v>
@@ -2392,10 +2392,10 @@
         <v>-16.8364</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4791</v>
+        <v>0.4791000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9162</v>
+        <v>0.9162000000000005</v>
       </c>
       <c r="Q25" t="n">
         <v>-17.4094</v>
@@ -2404,16 +2404,16 @@
         <v>18.3258</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7345</v>
+        <v>3.0169</v>
       </c>
       <c r="T25" t="n">
         <v>-1.1196</v>
       </c>
       <c r="U25" t="n">
-        <v>2.8543</v>
+        <v>4.136299999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.1466</v>
+        <v>-3.146600000000001</v>
       </c>
       <c r="W25" t="n">
         <v>3.2401</v>
